--- a/carteras.xlsx
+++ b/carteras.xlsx
@@ -1,34 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfried\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0EA9981-FED2-4D2D-A632-CA0FB2CB9FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Carteras" sheetId="1" r:id="rId1"/>
-    <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
+    <sheet name="Carteras" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -39,215 +23,217 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
   <si>
-    <t>Carteras sugeridas por moneda, perfil y horizonte</t>
-  </si>
-  <si>
-    <t>Los valores son el % objetivo de cada fondo dentro de la cartera. Cada fila debe sumar 100%. Editá solo las celdas azules; una celda vacía significa que ese fondo no entra en esa cartera.</t>
-  </si>
-  <si>
-    <t>FONDOS EN PESOS</t>
-  </si>
-  <si>
-    <t>FONDOS EN DÓLARES</t>
-  </si>
-  <si>
-    <t>Moneda</t>
-  </si>
-  <si>
-    <t>Perfil</t>
-  </si>
-  <si>
-    <t>Horizonte</t>
-  </si>
-  <si>
-    <t>Acciones</t>
-  </si>
-  <si>
-    <t>Ahorro corto plazo</t>
-  </si>
-  <si>
-    <t>Balanz Capital Pymes</t>
-  </si>
-  <si>
-    <t>Balanz Crecimiento</t>
-  </si>
-  <si>
-    <t>Balanz Crédito Privado</t>
-  </si>
-  <si>
-    <t>Balanz Infraestructura FCI</t>
-  </si>
-  <si>
-    <t>Balanz Long Pesos</t>
-  </si>
-  <si>
-    <t>Equity Selection</t>
-  </si>
-  <si>
-    <t>Inflation linked</t>
-  </si>
-  <si>
-    <t>Lecaps</t>
-  </si>
-  <si>
-    <t>Money Market</t>
-  </si>
-  <si>
-    <t>ONs</t>
-  </si>
-  <si>
-    <t>Opportunity</t>
-  </si>
-  <si>
-    <t>Renta Mixta</t>
-  </si>
-  <si>
-    <t>Soja</t>
-  </si>
-  <si>
-    <t>Balanz Money Market USD</t>
-  </si>
-  <si>
-    <t>Corporativo</t>
-  </si>
-  <si>
-    <t>Dolar Corto Plazo</t>
-  </si>
-  <si>
-    <t>Latam</t>
-  </si>
-  <si>
-    <t>Latam (SIN Arg)</t>
-  </si>
-  <si>
-    <t>Soberano</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Pesos</t>
-  </si>
-  <si>
-    <t>Conservador</t>
-  </si>
-  <si>
-    <t>&lt;1m</t>
-  </si>
-  <si>
-    <t>&lt;3m</t>
-  </si>
-  <si>
-    <t>&lt;6m</t>
-  </si>
-  <si>
-    <t>&lt;12m</t>
-  </si>
-  <si>
-    <t>&gt;12m</t>
-  </si>
-  <si>
-    <t>Moderado</t>
-  </si>
-  <si>
-    <t>Audaz</t>
-  </si>
-  <si>
-    <t>Dólar</t>
-  </si>
-  <si>
-    <t>Cómo editar este archivo</t>
-  </si>
-  <si>
-    <t>Este archivo es la única fuente de las carteras sugeridas que muestra la web. La página lo lee al cargar: si lo editás y lo subís al repositorio, las carteras cambian sin tocar código.</t>
-  </si>
-  <si>
-    <t>Qué se puede editar</t>
-  </si>
-  <si>
-    <t>•  Las celdas azules de la hoja "Carteras": el % objetivo de cada fondo en cada cartera.</t>
-  </si>
-  <si>
-    <t>•  Ya están todas las columnas de fondos disponibles, así que para sumar un fondo a una cartera solo hay que escribir su % en la columna que corresponde. Las columnas vacías no molestan.</t>
-  </si>
-  <si>
-    <t>•  Para sacar un fondo de una cartera, borrá el contenido de la celda.</t>
-  </si>
-  <si>
-    <t>Qué NO conviene tocar</t>
-  </si>
-  <si>
-    <t>•  La fila de encabezados (la que empieza con "Moneda"): la web busca los fondos por ese nombre.</t>
-  </si>
-  <si>
-    <t>•  El nombre de la hoja "Carteras".</t>
-  </si>
-  <si>
-    <t>•  Las columnas Moneda, Perfil y Horizonte: son valores cerrados, con lista desplegable. Si escribís otra cosa, la web ignora esa fila.</t>
-  </si>
-  <si>
-    <t>•  La columna Total: es una fórmula de control, no un dato.</t>
-  </si>
-  <si>
-    <t>Reglas que valida la web al cargar</t>
-  </si>
-  <si>
-    <t>•  Cada fila tiene que sumar 100%. La columna Total se pinta de rojo si no cierra, y la web muestra un aviso al elegir esa cartera.</t>
-  </si>
-  <si>
-    <t>•  Las 30 combinaciones (2 monedas × 3 perfiles × 5 horizontes) tienen que estar todas presentes.</t>
-  </si>
-  <si>
-    <t>•  Nada impide poner un fondo en pesos en una cartera de dólares: lo que define la moneda de la cartera es la columna Moneda de la fila, no el bloque en el que está la columna. Revisá que la combinación tenga sentido.</t>
-  </si>
-  <si>
-    <t>Valores admitidos</t>
-  </si>
-  <si>
-    <t>•  Moneda: Pesos · Dólar</t>
-  </si>
-  <si>
-    <t>•  Perfil: Conservador · Moderado · Audaz</t>
-  </si>
-  <si>
-    <t>•  Horizonte: &lt;1m · &lt;3m · &lt;6m · &lt;12m · &gt;12m</t>
-  </si>
-  <si>
-    <t>Formato de los porcentajes</t>
-  </si>
-  <si>
-    <t>Las celdas están formateadas como porcentaje. Escribí 50 o 50% y Excel lo guarda como 0,5, que la web lee como 50%. En la web los fondos se muestran ordenados de mayor a menor peso, sin importar el orden de las columnas.</t>
-  </si>
-  <si>
-    <t>Fondos que NO están como columna</t>
-  </si>
-  <si>
-    <t>Los fondos de categoría "Dedicados" y estos cuatro, que index.html descarta por lista propia: GLOBAL, Balanz Renta Fija Global, Dolar Linked, Balanz Desarrollo FCI. Agregarles una columna no serviría: la web los marcaría como "fondo no encontrado". Para poder usarlos hay que sacarlos antes de la constante EXCLUDED_FONDOS en index.html.</t>
-  </si>
-  <si>
-    <t>Cómo publicar un cambio</t>
-  </si>
-  <si>
-    <t>•  Guardá el archivo con el mismo nombre: carteras.xlsx</t>
-  </si>
-  <si>
-    <t>•  Subilo al repositorio de GitHub, en la misma carpeta que index.html</t>
-  </si>
-  <si>
-    <t>•  Vercel redeploya solo. Refrescá la web con Ctrl+Shift+R.</t>
-  </si>
-  <si>
-    <t>Columnas de fondos generadas desde data.csv: 15 en pesos y 6 en dólares.</t>
+    <t xml:space="preserve">Carteras sugeridas por moneda, perfil y horizonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los valores son el % objetivo de cada fondo dentro de la cartera. Cada fila debe sumar 100%. Editá solo las celdas azules; una celda vacía significa que ese fondo no entra en esa cartera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONDOS EN PESOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONDOS EN DÓLARES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moneda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro corto plazo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanz Capital Pymes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanz Crecimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanz Crédito Privado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanz Infraestructura FCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanz Long Pesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity Selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflation linked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecaps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opportunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renta Mixta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanz Money Market USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dolar Corto Plazo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latam (SIN Arg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soberano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conservador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;1m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;3m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;12m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;12m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dólar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cómo editar este archivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este archivo es la única fuente de las carteras sugeridas que muestra la web. La página lo lee al cargar: si lo editás y lo subís al repositorio, las carteras cambian sin tocar código.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qué se puede editar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Las celdas azules de la hoja "Carteras": el % objetivo de cada fondo en cada cartera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Ya están todas las columnas de fondos disponibles, así que para sumar un fondo a una cartera solo hay que escribir su % en la columna que corresponde. Las columnas vacías no molestan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Para sacar un fondo de una cartera, borrá el contenido de la celda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qué NO conviene tocar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  La fila de encabezados (la que empieza con "Moneda"): la web busca los fondos por ese nombre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  El nombre de la hoja "Carteras".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Las columnas Moneda, Perfil y Horizonte: son valores cerrados, con lista desplegable. Si escribís otra cosa, la web ignora esa fila.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  La columna Total: es una fórmula de control, no un dato.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reglas que valida la web al cargar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Cada fila tiene que sumar 100%. La columna Total se pinta de rojo si no cierra, y la web muestra un aviso al elegir esa cartera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Las 30 combinaciones (2 monedas × 3 perfiles × 5 horizontes) tienen que estar todas presentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Nada impide poner un fondo en pesos en una cartera de dólares: lo que define la moneda de la cartera es la columna Moneda de la fila, no el bloque en el que está la columna. Revisá que la combinación tenga sentido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valores admitidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Moneda: Pesos · Dólar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Perfil: Conservador · Moderado · Audaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Horizonte: &lt;1m · &lt;3m · &lt;6m · &lt;12m · &gt;12m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formato de los porcentajes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las celdas están formateadas como porcentaje. Escribí 50 o 50% y Excel lo guarda como 0,5, que la web lee como 50%. En la web los fondos se muestran ordenados de mayor a menor peso, sin importar el orden de las columnas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondos que NO están como columna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los fondos de categoría "Dedicados" y estos cuatro, que index.html descarta por lista propia: GLOBAL, Balanz Renta Fija Global, Dolar Linked, Balanz Desarrollo FCI. Agregarles una columna no serviría: la web los marcaría como "fondo no encontrado". Para poder usarlos hay que sacarlos antes de la constante EXCLUDED_FONDOS en index.html.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cómo publicar un cambio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Guardá el archivo con el mismo nombre: carteras.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Subilo al repositorio de GitHub, en la misma carpeta que index.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Vercel redeploya solo. Refrescá la web con Ctrl+Shift+R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columnas de fondos generadas desde data.csv: 15 en pesos y 6 en dólares.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0%;;\-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0%;;\-"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,71 +242,96 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="13"/>
       <color rgb="FF1B2559"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i/>
+      <i val="true"/>
       <sz val="9"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FF1B2559"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9.5"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF2C3A7B"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i/>
+      <i val="true"/>
       <sz val="8.5"/>
       <color rgb="FF777777"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,22 +374,16 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFC9D0E0"/>
       </left>
@@ -393,7 +398,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFC9D0E0"/>
       </left>
@@ -408,7 +413,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
         <color rgb="FF1B2559"/>
       </left>
@@ -424,74 +429,126 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="19">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C0006"/>
         <name val="Arial"/>
         <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+        <sz val="9"/>
       </font>
       <fill>
         <patternFill>
@@ -500,7 +557,6 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -559,63 +615,47 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2C3A7B"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -623,12 +663,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -657,7 +697,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -678,7 +718,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -729,7 +769,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -747,66 +787,67 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="24" width="10.5546875" customWidth="1"/>
-    <col min="25" max="25" width="8" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="4" style="0" width="10.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="D3" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="1" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-    </row>
-    <row r="4" spans="1:25" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -883,7 +924,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>29</v>
       </c>
@@ -903,25 +944,25 @@
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="10">
+      <c r="N5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="11">
-        <f>SUM($D5:INDEX($5:$5,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="11" t="n">
+        <f aca="false">SUM($D5:INDEX($5:$5,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
@@ -932,7 +973,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="10">
+      <c r="E6" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="F6" s="10"/>
@@ -943,25 +984,25 @@
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
-      <c r="N6" s="10">
+      <c r="N6" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="11">
-        <f>SUM($D6:INDEX($6:$6,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="11" t="n">
+        <f aca="false">SUM($D6:INDEX($6:$6,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
@@ -972,7 +1013,7 @@
         <v>33</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="10">
+      <c r="E7" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="F7" s="10"/>
@@ -984,24 +1025,24 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
-      <c r="O7" s="10">
+      <c r="O7" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="11">
-        <f>SUM($D7:INDEX($7:$7,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="11" t="n">
+        <f aca="false">SUM($D7:INDEX($7:$7,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>29</v>
       </c>
@@ -1012,8 +1053,8 @@
         <v>34</v>
       </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="10">
-        <v>0.2</v>
+      <c r="E8" s="10" t="n">
+        <v>0.25</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
@@ -1021,29 +1062,29 @@
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="10">
-        <v>0.6</v>
+      <c r="L8" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
-      <c r="O8" s="10">
-        <v>0.2</v>
+      <c r="O8" s="10" t="n">
+        <v>0.25</v>
       </c>
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="11">
-        <f>SUM($D8:INDEX($8:$8,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="11" t="n">
+        <f aca="false">SUM($D8:INDEX($8:$8,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
@@ -1061,31 +1102,31 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="10">
+      <c r="L9" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
-      <c r="O9" s="10">
+      <c r="O9" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="11">
-        <f>SUM($D9:INDEX($9:$9,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="11" t="n">
+        <f aca="false">SUM($D9:INDEX($9:$9,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
         <v>29</v>
       </c>
@@ -1096,7 +1137,9 @@
         <v>31</v>
       </c>
       <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+      <c r="E10" s="10" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -1105,25 +1148,25 @@
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
-      <c r="N10" s="10">
-        <v>1</v>
+      <c r="N10" s="10" t="n">
+        <v>0.75</v>
       </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="11">
-        <f>SUM($D10:INDEX($10:$10,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="11" t="n">
+        <f aca="false">SUM($D10:INDEX($10:$10,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
@@ -1134,7 +1177,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="10">
+      <c r="E11" s="10" t="n">
         <v>0.75</v>
       </c>
       <c r="F11" s="10"/>
@@ -1145,25 +1188,25 @@
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
-      <c r="N11" s="10">
+      <c r="N11" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="11">
-        <f>SUM($D11:INDEX($11:$11,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="11" t="n">
+        <f aca="false">SUM($D11:INDEX($11:$11,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
         <v>29</v>
       </c>
@@ -1174,7 +1217,7 @@
         <v>33</v>
       </c>
       <c r="D12" s="10"/>
-      <c r="E12" s="10">
+      <c r="E12" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="F12" s="10"/>
@@ -1183,7 +1226,7 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
-      <c r="L12" s="10">
+      <c r="L12" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="M12" s="10"/>
@@ -1192,18 +1235,18 @@
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="11">
-        <f>SUM($D12:INDEX($12:$12,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="11" t="n">
+        <f aca="false">SUM($D12:INDEX($12:$12,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
@@ -1221,31 +1264,31 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="10">
+      <c r="L13" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
-      <c r="O13" s="10">
+      <c r="O13" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="11">
-        <f>SUM($D13:INDEX($13:$13,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="11" t="n">
+        <f aca="false">SUM($D13:INDEX($13:$13,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
         <v>29</v>
       </c>
@@ -1263,29 +1306,31 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
-      <c r="L14" s="10">
+      <c r="L14" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
-      <c r="P14" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="Q14" s="10"/>
+      <c r="P14" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q14" s="10" t="n">
+        <v>0.25</v>
+      </c>
       <c r="R14" s="10"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="19"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="11">
-        <f>SUM($D14:INDEX($14:$14,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="11" t="n">
+        <f aca="false">SUM($D14:INDEX($14:$14,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
@@ -1296,7 +1341,9 @@
         <v>31</v>
       </c>
       <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="E15" s="10" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -1304,28 +1351,28 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="N15" s="10">
+      <c r="M15" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N15" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="11">
-        <f>SUM($D15:INDEX($15:$15,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="11" t="n">
+        <f aca="false">SUM($D15:INDEX($15:$15,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
         <v>29</v>
       </c>
@@ -1336,8 +1383,8 @@
         <v>32</v>
       </c>
       <c r="D16" s="10"/>
-      <c r="E16" s="10">
-        <v>0.5</v>
+      <c r="E16" s="10" t="n">
+        <v>0.75</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1346,26 +1393,26 @@
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="10">
-        <v>0.5</v>
+      <c r="M16" s="10" t="n">
+        <v>0.25</v>
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="11">
-        <f>SUM($D16:INDEX($16:$16,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="11" t="n">
+        <f aca="false">SUM($D16:INDEX($16:$16,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
         <v>29</v>
       </c>
@@ -1376,7 +1423,7 @@
         <v>33</v>
       </c>
       <c r="D17" s="10"/>
-      <c r="E17" s="10">
+      <c r="E17" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="F17" s="10"/>
@@ -1385,10 +1432,10 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
-      <c r="L17" s="10">
+      <c r="L17" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="N17" s="10"/>
@@ -1396,18 +1443,18 @@
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="11">
-        <f>SUM($D17:INDEX($17:$17,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="11" t="n">
+        <f aca="false">SUM($D17:INDEX($17:$17,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
@@ -1425,31 +1472,31 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
-      <c r="L18" s="10">
+      <c r="L18" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
-      <c r="P18" s="10">
+      <c r="P18" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="Q18" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="R18" s="10"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="11">
-        <f>SUM($D18:INDEX($18:$18,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="11" t="n">
+        <f aca="false">SUM($D18:INDEX($18:$18,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
         <v>29</v>
       </c>
@@ -1465,31 +1512,33 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="K19" s="10">
-        <v>0.5</v>
+      <c r="J19" s="10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0.34</v>
       </c>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
+      <c r="Q19" s="10" t="n">
+        <v>0.33</v>
+      </c>
       <c r="R19" s="10"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="11">
-        <f>SUM($D19:INDEX($19:$19,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="11" t="n">
+        <f aca="false">SUM($D19:INDEX($19:$19,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
         <v>38</v>
       </c>
@@ -1499,22 +1548,22 @@
       <c r="C20" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="10">
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10" t="n">
         <v>1</v>
       </c>
       <c r="T20" s="10"/>
@@ -1522,12 +1571,12 @@
       <c r="V20" s="10"/>
       <c r="W20" s="10"/>
       <c r="X20" s="10"/>
-      <c r="Y20" s="11">
-        <f>SUM($D20:INDEX($20:$20,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y20" s="11" t="n">
+        <f aca="false">SUM($D20:INDEX($20:$20,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
         <v>38</v>
       </c>
@@ -1537,35 +1586,37 @@
       <c r="C21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="10">
-        <v>1</v>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10" t="n">
+        <v>0.75</v>
       </c>
       <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
+      <c r="U21" s="10" t="n">
+        <v>0.25</v>
+      </c>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
       <c r="X21" s="10"/>
-      <c r="Y21" s="11">
-        <f>SUM($D21:INDEX($21:$21,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y21" s="11" t="n">
+        <f aca="false">SUM($D21:INDEX($21:$21,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
         <v>38</v>
       </c>
@@ -1575,37 +1626,37 @@
       <c r="C22" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="10">
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="T22" s="10"/>
-      <c r="U22" s="10">
+      <c r="U22" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="V22" s="10"/>
       <c r="W22" s="10"/>
       <c r="X22" s="10"/>
-      <c r="Y22" s="11">
-        <f>SUM($D22:INDEX($22:$22,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y22" s="11" t="n">
+        <f aca="false">SUM($D22:INDEX($22:$22,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
         <v>38</v>
       </c>
@@ -1615,35 +1666,35 @@
       <c r="C23" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
-      <c r="U23" s="10">
+      <c r="U23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="V23" s="10"/>
       <c r="W23" s="10"/>
       <c r="X23" s="10"/>
-      <c r="Y23" s="11">
-        <f>SUM($D23:INDEX($23:$23,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y23" s="11" t="n">
+        <f aca="false">SUM($D23:INDEX($23:$23,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
         <v>38</v>
       </c>
@@ -1653,37 +1704,37 @@
       <c r="C24" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
-      <c r="U24" s="10">
+      <c r="U24" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="V24" s="10">
+      <c r="V24" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="W24" s="10"/>
       <c r="X24" s="10"/>
-      <c r="Y24" s="11">
-        <f>SUM($D24:INDEX($24:$24,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y24" s="11" t="n">
+        <f aca="false">SUM($D24:INDEX($24:$24,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
         <v>38</v>
       </c>
@@ -1693,35 +1744,37 @@
       <c r="C25" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="10">
-        <v>1</v>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10" t="n">
+        <v>0.75</v>
       </c>
       <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
+      <c r="U25" s="10" t="n">
+        <v>0.25</v>
+      </c>
       <c r="V25" s="10"/>
       <c r="W25" s="10"/>
       <c r="X25" s="10"/>
-      <c r="Y25" s="11">
-        <f>SUM($D25:INDEX($25:$25,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y25" s="11" t="n">
+        <f aca="false">SUM($D25:INDEX($25:$25,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
         <v>38</v>
       </c>
@@ -1731,37 +1784,37 @@
       <c r="C26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="10">
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="T26" s="10"/>
-      <c r="U26" s="10">
+      <c r="U26" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="V26" s="10"/>
       <c r="W26" s="10"/>
       <c r="X26" s="10"/>
-      <c r="Y26" s="11">
-        <f>SUM($D26:INDEX($26:$26,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y26" s="11" t="n">
+        <f aca="false">SUM($D26:INDEX($26:$26,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
         <v>38</v>
       </c>
@@ -1771,35 +1824,35 @@
       <c r="C27" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
-      <c r="U27" s="10">
+      <c r="U27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="V27" s="10"/>
       <c r="W27" s="10"/>
       <c r="X27" s="10"/>
-      <c r="Y27" s="11">
-        <f>SUM($D27:INDEX($27:$27,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y27" s="11" t="n">
+        <f aca="false">SUM($D27:INDEX($27:$27,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
         <v>38</v>
       </c>
@@ -1809,39 +1862,37 @@
       <c r="C28" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
       <c r="S28" s="10"/>
-      <c r="T28" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="U28" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="V28" s="10">
+      <c r="T28" s="10"/>
+      <c r="U28" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V28" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="W28" s="10"/>
       <c r="X28" s="10"/>
-      <c r="Y28" s="11">
-        <f>SUM($D28:INDEX($28:$28,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y28" s="11" t="n">
+        <f aca="false">SUM($D28:INDEX($28:$28,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
         <v>38</v>
       </c>
@@ -1851,39 +1902,39 @@
       <c r="C29" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
       <c r="S29" s="10"/>
-      <c r="T29" s="10">
+      <c r="T29" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="U29" s="10">
+      <c r="U29" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="V29" s="10">
+      <c r="V29" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="W29" s="10"/>
       <c r="X29" s="10"/>
-      <c r="Y29" s="11">
-        <f>SUM($D29:INDEX($29:$29,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y29" s="11" t="n">
+        <f aca="false">SUM($D29:INDEX($29:$29,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
         <v>38</v>
       </c>
@@ -1893,35 +1944,37 @@
       <c r="C30" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="10">
-        <v>1</v>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
+      <c r="U30" s="10" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V30" s="10"/>
       <c r="W30" s="10"/>
       <c r="X30" s="10"/>
-      <c r="Y30" s="11">
-        <f>SUM($D30:INDEX($30:$30,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y30" s="11" t="n">
+        <f aca="false">SUM($D30:INDEX($30:$30,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
         <v>38</v>
       </c>
@@ -1931,35 +1984,35 @@
       <c r="C31" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
       <c r="S31" s="10"/>
       <c r="T31" s="10"/>
-      <c r="U31" s="10">
+      <c r="U31" s="10" t="n">
         <v>1</v>
       </c>
       <c r="V31" s="10"/>
       <c r="W31" s="10"/>
       <c r="X31" s="10"/>
-      <c r="Y31" s="11">
-        <f>SUM($D31:INDEX($31:$31,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y31" s="11" t="n">
+        <f aca="false">SUM($D31:INDEX($31:$31,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
         <v>38</v>
       </c>
@@ -1969,39 +2022,37 @@
       <c r="C32" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
       <c r="S32" s="10"/>
-      <c r="T32" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="U32" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="V32" s="10">
+      <c r="T32" s="10"/>
+      <c r="U32" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V32" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="W32" s="10"/>
       <c r="X32" s="10"/>
-      <c r="Y32" s="11">
-        <f>SUM($D32:INDEX($32:$32,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y32" s="11" t="n">
+        <f aca="false">SUM($D32:INDEX($32:$32,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
         <v>38</v>
       </c>
@@ -2011,39 +2062,39 @@
       <c r="C33" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
       <c r="S33" s="10"/>
-      <c r="T33" s="10">
+      <c r="T33" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U33" s="10">
+      <c r="U33" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="V33" s="10">
+      <c r="V33" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="W33" s="10"/>
       <c r="X33" s="10"/>
-      <c r="Y33" s="11">
-        <f>SUM($D33:INDEX($33:$33,COLUMN()-1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Y33" s="11" t="n">
+        <f aca="false">SUM($D33:INDEX($33:$33,COLUMN()-1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
         <v>38</v>
       </c>
@@ -2053,33 +2104,33 @@
       <c r="C34" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
       <c r="S34" s="10"/>
-      <c r="T34" s="10">
+      <c r="T34" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="U34" s="10"/>
       <c r="V34" s="10"/>
       <c r="W34" s="10"/>
-      <c r="X34" s="10">
+      <c r="X34" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y34" s="11">
-        <f>SUM($D34:INDEX($34:$34,COLUMN()-1))</f>
+      <c r="Y34" s="11" t="n">
+        <f aca="false">SUM($D34:INDEX($34:$34,COLUMN()-1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2089,180 +2140,481 @@
     <mergeCell ref="S3:X3"/>
   </mergeCells>
   <conditionalFormatting sqref="Y5:Y34">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
+    <cfRule type="cellIs" priority="2" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" errorTitle="Valor inválido" error="Valor no reconocido por la web. Usá uno de la lista." sqref="A5:A34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation allowBlank="false" error="Valor no reconocido por la web. Usá uno de la lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A5:A34" type="list">
       <formula1>"Pesos,Dólar"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" errorTitle="Valor inválido" error="Valor no reconocido por la web. Usá uno de la lista." sqref="B5:B34" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation allowBlank="false" error="Valor no reconocido por la web. Usá uno de la lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B34" type="list">
       <formula1>"Conservador,Moderado,Audaz"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" errorTitle="Valor inválido" error="Valor no reconocido por la web. Usá uno de la lista." sqref="C5:C34" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation allowBlank="false" error="Valor no reconocido por la web. Usá uno de la lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C34" type="list">
       <formula1>"&lt;1m,&lt;3m,&lt;6m,&lt;12m,&gt;12m"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:B41"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="112" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="112"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="24" x14ac:dyDescent="0.3">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="24" x14ac:dyDescent="0.3">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="24" x14ac:dyDescent="0.3">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="24" x14ac:dyDescent="0.3">
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="36" x14ac:dyDescent="0.3">
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="16" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="18" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
+    <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
+    <xsd:import namespace="b80a8b0a-2819-4368-b347-46490e6c629e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="14def1a7-4a65-4794-a890-bf5d96e78463" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="_Flow_SignoffStatus" ma:index="23" nillable="true" ma:displayName="Sign-off status" ma:internalName="Sign_x002d_off_x0020_status">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b80a8b0a-2819-4368-b347-46490e6c629e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{533d0a59-4079-4776-b0c6-0cef15366990}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b80a8b0a-2819-4368-b347-46490e6c629e">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADAFB8CD-4B98-4B9F-9279-96B614C84C0B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23198D48-46D5-4D70-AEDE-ED4B69E58775}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B6D4DB8-4C05-42D1-8C1B-DBF71041FFD4}"/>
 </file>